--- a/data/trans_orig/Q5412-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5412-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de arreglarse en 2007</t>
+          <t>Población según si es capaz de arreglarse en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9021</t>
+          <t>8606</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22876</t>
+          <t>22066</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15875</t>
+          <t>16288</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36168</t>
+          <t>35942</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29120</t>
+          <t>28485</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54290</t>
+          <t>54345</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>350313</t>
+          <t>351123</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>364168</t>
+          <t>364583</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>551581</t>
+          <t>551807</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>571874</t>
+          <t>571461</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>906648</t>
+          <t>906593</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>931818</t>
+          <t>932453</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>824</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8397</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83994</t>
+          <t>83871</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55108</t>
+          <t>54942</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>141928</t>
+          <t>141898</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>149496</t>
+          <t>149471</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -1419,97 +1419,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39010</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41194</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25052</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66007</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>68075</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23913</t>
+          <t>23707</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18436</t>
+          <t>18336</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40086</t>
+          <t>39283</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31886</t>
+          <t>32339</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56551</t>
+          <t>57103</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>478553</t>
+          <t>478759</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>493346</t>
+          <t>492669</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>636756</t>
+          <t>637559</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>658406</t>
+          <t>658506</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1122757</t>
+          <t>1122205</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1147422</t>
+          <t>1146969</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de arreglarse en 2012</t>
+          <t>Población según si es capaz de arreglarse en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19172</t>
+          <t>18720</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41442</t>
+          <t>41995</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56759</t>
+          <t>56148</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89014</t>
+          <t>89774</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80859</t>
+          <t>81283</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120365</t>
+          <t>121879</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>372956</t>
+          <t>372403</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>395226</t>
+          <t>395678</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>545531</t>
+          <t>544771</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>577786</t>
+          <t>578397</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>928577</t>
+          <t>927063</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>968083</t>
+          <t>967659</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,25%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12880</t>
+          <t>13510</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>999</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10441</t>
+          <t>10373</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18981</t>
+          <t>18647</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>105785</t>
+          <t>105155</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>116398</t>
+          <t>116511</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72633</t>
+          <t>72701</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>81750</t>
+          <t>82075</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>182758</t>
+          <t>183092</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>196623</t>
+          <t>196389</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -3022,97 +3022,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5753</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>25,86%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1100</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5031</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5529</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>22,61%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4900</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24279</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26575</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17215</t>
+          <t>16493</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43921</t>
+          <t>43292</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25195</t>
+          <t>23922</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49738</t>
+          <t>47916</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60443</t>
+          <t>60910</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96786</t>
+          <t>95432</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91517</t>
+          <t>90292</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135771</t>
+          <t>132221</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>509899</t>
+          <t>511721</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>534442</t>
+          <t>535715</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>643079</t>
+          <t>644433</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>679422</t>
+          <t>678955</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1163731</t>
+          <t>1167281</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1207985</t>
+          <t>1209210</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,05%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de arreglarse en 2016</t>
+          <t>Población según si es capaz de arreglarse en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>12130</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28638</t>
+          <t>28346</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32405</t>
+          <t>32979</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61658</t>
+          <t>61794</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49427</t>
+          <t>50561</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82473</t>
+          <t>84789</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>325263</t>
+          <t>325555</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>341551</t>
+          <t>341771</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>493099</t>
+          <t>492963</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>522352</t>
+          <t>521778</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>826185</t>
+          <t>823869</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>859231</t>
+          <t>858097</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,44%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>881</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16702</t>
+          <t>18038</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5038</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21366</t>
+          <t>20671</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>185034</t>
+          <t>184233</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>191763</t>
+          <t>191651</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>171372</t>
+          <t>170036</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>184977</t>
+          <t>184971</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>359240</t>
+          <t>359935</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>375568</t>
+          <t>375990</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -4625,97 +4625,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40117</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42029</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31298</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33674</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>73571</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>75703</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14290</t>
+          <t>14446</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32080</t>
+          <t>32162</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39232</t>
+          <t>39158</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70517</t>
+          <t>70879</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58231</t>
+          <t>58419</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93929</t>
+          <t>93998</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>556383</t>
+          <t>556301</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>574173</t>
+          <t>574017</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>705988</t>
+          <t>705626</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>737273</t>
+          <t>737347</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1271039</t>
+          <t>1270970</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1306737</t>
+          <t>1306549</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de arreglarse en 2023</t>
+          <t>Población según si es capaz de arreglarse en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15348</t>
+          <t>15146</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28409</t>
+          <t>29599</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59600</t>
+          <t>59073</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81334</t>
+          <t>81682</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79919</t>
+          <t>79929</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106266</t>
+          <t>106733</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>240835</t>
+          <t>239645</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>253896</t>
+          <t>254098</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>419048</t>
+          <t>418700</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>440782</t>
+          <t>441309</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>663359</t>
+          <t>662892</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>689706</t>
+          <t>689696</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,61%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15024</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3508</t>
+          <t>3371</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23912</t>
+          <t>23056</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8798</t>
+          <t>8384</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31869</t>
+          <t>32568</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>258233</t>
+          <t>258207</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>268121</t>
+          <t>268087</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>431827</t>
+          <t>432683</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>452231</t>
+          <t>452368</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>697127</t>
+          <t>696428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>720198</t>
+          <t>720612</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,62 +6263,62 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>775</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3211</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>775</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3585</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>101709</t>
+          <t>101156</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104836</t>
+          <t>104986</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70431</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>172726</t>
+          <t>173100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23768</t>
+          <t>23965</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41904</t>
+          <t>41287</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40606</t>
+          <t>40837</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>107746</t>
+          <t>108356</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73257</t>
+          <t>74615</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>137092</t>
+          <t>134998</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>605583</t>
+          <t>606200</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>623719</t>
+          <t>623522</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>919700</t>
+          <t>919090</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>986840</t>
+          <t>986609</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1537840</t>
+          <t>1539934</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1601675</t>
+          <t>1600317</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5412-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5412-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8606</t>
+          <t>8286</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22066</t>
+          <t>22799</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16288</t>
+          <t>16797</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35942</t>
+          <t>37153</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28485</t>
+          <t>28644</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54345</t>
+          <t>53574</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>351123</t>
+          <t>350390</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>364583</t>
+          <t>364903</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>551807</t>
+          <t>550596</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>571461</t>
+          <t>570952</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>906593</t>
+          <t>907364</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>932453</t>
+          <t>932294</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>6953</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>814</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8397</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83871</t>
+          <t>83918</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54942</t>
+          <t>55259</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>141898</t>
+          <t>141236</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>149471</t>
+          <t>149481</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23707</t>
+          <t>24848</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18336</t>
+          <t>18554</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39283</t>
+          <t>40174</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32339</t>
+          <t>31094</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57103</t>
+          <t>57075</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>478759</t>
+          <t>477618</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>492669</t>
+          <t>492565</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>637559</t>
+          <t>636668</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>658506</t>
+          <t>658288</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1122205</t>
+          <t>1122233</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1146969</t>
+          <t>1148214</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18720</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41995</t>
+          <t>40328</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56148</t>
+          <t>55070</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89774</t>
+          <t>90732</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81283</t>
+          <t>81802</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121879</t>
+          <t>122533</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>372403</t>
+          <t>374070</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>395678</t>
+          <t>395392</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>544771</t>
+          <t>543813</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>578397</t>
+          <t>579475</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>927063</t>
+          <t>926409</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>967659</t>
+          <t>967140</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,2%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>2187</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13510</t>
+          <t>12585</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10373</t>
+          <t>10441</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18647</t>
+          <t>18583</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>105155</t>
+          <t>106080</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>116511</t>
+          <t>116478</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72701</t>
+          <t>72633</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82075</t>
+          <t>81959</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>183092</t>
+          <t>183156</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>196389</t>
+          <t>196503</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16493</t>
+          <t>15417</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43292</t>
+          <t>43035</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23922</t>
+          <t>23993</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47916</t>
+          <t>47952</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60910</t>
+          <t>61533</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95432</t>
+          <t>96276</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90292</t>
+          <t>93376</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132221</t>
+          <t>135533</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>511721</t>
+          <t>511685</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>535715</t>
+          <t>535644</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>644433</t>
+          <t>643589</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>678955</t>
+          <t>678332</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1167281</t>
+          <t>1163969</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1209210</t>
+          <t>1206126</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12130</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28346</t>
+          <t>28926</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32979</t>
+          <t>33737</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61794</t>
+          <t>61760</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50561</t>
+          <t>48907</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84789</t>
+          <t>81636</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>325555</t>
+          <t>324975</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>341771</t>
+          <t>341040</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>492963</t>
+          <t>492997</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>521778</t>
+          <t>521020</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>823869</t>
+          <t>827022</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>858097</t>
+          <t>859751</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>895</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8003</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18038</t>
+          <t>17066</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20671</t>
+          <t>20669</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>184233</t>
+          <t>184529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>191651</t>
+          <t>191637</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>170036</t>
+          <t>171008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>184971</t>
+          <t>185718</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>359935</t>
+          <t>359937</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>375990</t>
+          <t>376107</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14446</t>
+          <t>14466</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32162</t>
+          <t>31569</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39158</t>
+          <t>39471</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70879</t>
+          <t>72063</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58419</t>
+          <t>59120</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93998</t>
+          <t>95954</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>556301</t>
+          <t>556894</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>574017</t>
+          <t>573997</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>705626</t>
+          <t>704442</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>737347</t>
+          <t>737034</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1270970</t>
+          <t>1269014</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1306549</t>
+          <t>1305848</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>21456</t>
+          <t>22716</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15146</t>
+          <t>15911</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29599</t>
+          <t>30807</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,67 +5572,67 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>70441</t>
+          <t>75143</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59073</t>
+          <t>63131</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81682</t>
+          <t>86921</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>11,73%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>16,14%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>97859</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>84172</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>112018</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>11,81%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>16,32%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>91897</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>79929</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>106733</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>11,94%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>247788</t>
+          <t>267379</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>239645</t>
+          <t>259288</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>254098</t>
+          <t>274184</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,67 +5685,67 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>429941</t>
+          <t>463260</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>418700</t>
+          <t>451482</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>441309</t>
+          <t>475272</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>88,27%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1266</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>730639</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>716480</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>744326</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>88,19%</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1266</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>677728</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>662892</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>689696</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>88,06%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,84%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>500382</t>
+          <t>538403</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>500382</t>
+          <t>538403</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>500382</t>
+          <t>538403</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>769625</t>
+          <t>828498</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>769625</t>
+          <t>828498</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>769625</t>
+          <t>828498</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,27 +5880,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>9658</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>16747</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11341</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>7874</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23056</t>
+          <t>18056</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>20614</t>
+          <t>21799</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32568</t>
+          <t>30122</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -5993,22 +5993,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>263984</t>
+          <t>294167</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>258207</t>
+          <t>287078</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>268087</t>
+          <t>297923</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>444398</t>
+          <t>265505</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>432683</t>
+          <t>259590</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>452368</t>
+          <t>269772</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>708382</t>
+          <t>559672</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>696428</t>
+          <t>551349</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>720612</t>
+          <t>566018</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>4297</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -6336,27 +6336,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>104211</t>
+          <t>117621</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>101156</t>
+          <t>114584</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -6406,27 +6406,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>175536</t>
+          <t>200476</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>173100</t>
+          <t>197275</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31505</t>
+          <t>33634</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23965</t>
+          <t>25136</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41287</t>
+          <t>44688</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>81781</t>
+          <t>87283</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40837</t>
+          <t>75151</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108356</t>
+          <t>100837</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>113286</t>
+          <t>120917</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74615</t>
+          <t>105470</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134998</t>
+          <t>137511</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>615982</t>
+          <t>679167</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>606200</t>
+          <t>668113</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>623522</t>
+          <t>687665</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>945665</t>
+          <t>811621</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>919090</t>
+          <t>798067</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>986609</t>
+          <t>823753</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1561646</t>
+          <t>1490788</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1539934</t>
+          <t>1474194</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1600317</t>
+          <t>1506235</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>93,46%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1027446</t>
+          <t>898904</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1027446</t>
+          <t>898904</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1027446</t>
+          <t>898904</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1674932</t>
+          <t>1611705</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1674932</t>
+          <t>1611705</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1674932</t>
+          <t>1611705</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
